--- a/doc/需求.xlsx
+++ b/doc/需求.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B678AA-61F7-4E32-A6D0-2C3E85A68802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22A4D27-A6F4-4915-83EA-DF8D93C9DC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="1" r:id="rId1"/>
@@ -78,634 +78,635 @@
     <t>本地预览与写作</t>
   </si>
   <si>
+    <t>http://localhost:4000/</t>
+  </si>
+  <si>
+    <t>写完文章 push main 触发 Actions 自动发布</t>
+  </si>
+  <si>
+    <t>自动发布</t>
+  </si>
+  <si>
+    <t>GitHub Actions 构建并发布到 GitHub Pages</t>
+  </si>
+  <si>
+    <t>.github/workflows/pages.yml</t>
+  </si>
+  <si>
+    <t>线上站点</t>
+  </si>
+  <si>
+    <t>push main 自动发布；PR 仅构建验证</t>
+  </si>
+  <si>
+    <t>路径</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>归类</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>示例/关键点</t>
+  </si>
+  <si>
+    <t>是否发布(Y/N)</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>/source/_posts/</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>文章 Markdown（可按年份分目录）</t>
+  </si>
+  <si>
+    <t>source/_posts/2026/2026-02-09-lei-xing-cun-zhe-you-xi.md</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>post_asset_folder=true 时，文章资源目录与 md 同级</t>
+  </si>
+  <si>
+    <t>/source/img/</t>
+  </si>
+  <si>
+    <t>全站静态图片（非文章私有资源）</t>
+  </si>
+  <si>
+    <t>首页 banner、头像、通用配图</t>
+  </si>
+  <si>
+    <t>适合被多篇文章复用的资源</t>
+  </si>
+  <si>
+    <t>/source/css/custom.css</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>自定义样式（字体/动态背景/深色模式等）</t>
+  </si>
+  <si>
+    <t>通过主题 inject 引入</t>
+  </si>
+  <si>
+    <t>路径为 /css/custom.css</t>
+  </si>
+  <si>
+    <t>/source/js/cloud-bg.js</t>
+  </si>
+  <si>
+    <t>动态背景脚本（页面类型识别 + PJAX 兼容）</t>
+  </si>
+  <si>
+    <t>路径为 /js/cloud-bg.js</t>
+  </si>
+  <si>
+    <t>/_config.yml</t>
+  </si>
+  <si>
+    <t>配置</t>
+  </si>
+  <si>
+    <t>Hexo 主配置</t>
+  </si>
+  <si>
+    <t>url=https://yurisachan16-creator.github.io; permalink=:year/:month/:day/:title/</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>改动会影响全站生成与路径</t>
+  </si>
+  <si>
+    <t>/_config.butterfly.yml</t>
+  </si>
+  <si>
+    <t>Butterfly 主题配置</t>
+  </si>
+  <si>
+    <t>menu、cover、inject、自定义资源</t>
+  </si>
+  <si>
+    <t>控制首页封面、导航菜单、注入资源等</t>
+  </si>
+  <si>
+    <t>/.github/workflows/pages.yml</t>
+  </si>
+  <si>
+    <t>自动化</t>
+  </si>
+  <si>
+    <t>Pages 构建与发布工作流</t>
+  </si>
+  <si>
+    <t>npm ci → npm run build → upload public</t>
+  </si>
+  <si>
+    <t>仓库 Settings → Pages 需要选择 GitHub Actions</t>
+  </si>
+  <si>
+    <t>/tools/</t>
+  </si>
+  <si>
+    <t>工具</t>
+  </si>
+  <si>
+    <t>本地脚本（不会发布到站点）</t>
+  </si>
+  <si>
+    <t>图片处理脚本、主题同步脚本等</t>
+  </si>
+  <si>
+    <t>不要把工具脚本放到 source/ 里</t>
+  </si>
+  <si>
+    <t>/doc/需求.xlsx</t>
+  </si>
+  <si>
+    <t>文档</t>
+  </si>
+  <si>
+    <t>结构/规范/扩展记录表</t>
+  </si>
+  <si>
+    <t>本脚本自动写入更新</t>
+  </si>
+  <si>
+    <t>本次生成时间：2026-02-14 00:04:05</t>
+  </si>
+  <si>
+    <t>/_config.butterfly.yml#menu</t>
+  </si>
+  <si>
+    <t>config</t>
+  </si>
+  <si>
+    <t>导航菜单项</t>
+  </si>
+  <si>
+    <t>首页: / || fas fa-home</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>归档: /archives/ || fas fa-archive</t>
+  </si>
+  <si>
+    <t>标签: /tags/ || fas fa-tags</t>
+  </si>
+  <si>
+    <t>分类: /categories/ || fas fa-folder-open</t>
+  </si>
+  <si>
+    <t>关于: /about/ || fas fa-heart</t>
+  </si>
+  <si>
+    <t>接口类型</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>入口（命令/文件#键）</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>输出/影响</t>
+  </si>
+  <si>
+    <t>常见问题/排查</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>本地预览</t>
+  </si>
+  <si>
+    <t>npm run server</t>
+  </si>
+  <si>
+    <t>source/ + 配置</t>
+  </si>
+  <si>
+    <t>端口被占用/依赖未装/主题未同步</t>
+  </si>
+  <si>
+    <t>生成静态站点</t>
+  </si>
+  <si>
+    <t>npm run build</t>
+  </si>
+  <si>
+    <t>封面/图片路径写成相对路径导致首页 404</t>
+  </si>
+  <si>
+    <t>清理缓存</t>
+  </si>
+  <si>
+    <t>npm run clean</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>清理 db.json 与 public 等缓存</t>
+  </si>
+  <si>
+    <t>生成异常时优先 clean 后再 build</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Actions 构建与发布</t>
+  </si>
+  <si>
+    <t>.github/workflows/pages.yml (push main)</t>
+  </si>
+  <si>
+    <t>main 分支源码</t>
+  </si>
+  <si>
+    <t>GitHub Pages</t>
+  </si>
+  <si>
+    <t>Settings→Pages 未设为 GitHub Actions/依赖安装失败/生成失败</t>
+  </si>
+  <si>
+    <t>永久链接规则</t>
+  </si>
+  <si>
+    <t>_config.yml#permalink</t>
+  </si>
+  <si>
+    <t>文章 date/title</t>
+  </si>
+  <si>
+    <t>文章 URL 结构</t>
+  </si>
+  <si>
+    <t>改规则会影响历史链接；可用 front-matter permalink 固定单篇路径</t>
+  </si>
+  <si>
+    <t>文章资源文件夹</t>
+  </si>
+  <si>
+    <t>_config.yml#post_asset_folder</t>
+  </si>
+  <si>
+    <t>文章同名目录资源</t>
+  </si>
+  <si>
+    <t>生成到 public 的文章资源</t>
+  </si>
+  <si>
+    <t>资源目录需与文章 md 同级；封面建议用以 / 开头的绝对路径</t>
+  </si>
+  <si>
+    <t>Front-matter</t>
+  </si>
+  <si>
+    <t>封面 cover</t>
+  </si>
+  <si>
+    <t>post.md front-matter#cover</t>
+  </si>
+  <si>
+    <t>图片路径</t>
+  </si>
+  <si>
+    <t>首页卡片封面/文章页封面</t>
+  </si>
+  <si>
+    <t>推荐使用站点绝对路径，如 /2026/02/09/.../cover.jpg</t>
+  </si>
+  <si>
+    <t>npm script: build</t>
+  </si>
+  <si>
+    <t>package.json#scripts.build</t>
+  </si>
+  <si>
+    <t>hexo generate</t>
+  </si>
+  <si>
+    <t>npm script: clean</t>
+  </si>
+  <si>
+    <t>package.json#scripts.clean</t>
+  </si>
+  <si>
+    <t>hexo clean</t>
+  </si>
+  <si>
+    <t>npm script: deploy</t>
+  </si>
+  <si>
+    <t>package.json#scripts.deploy</t>
+  </si>
+  <si>
+    <t>hexo deploy</t>
+  </si>
+  <si>
+    <t>npm script: server</t>
+  </si>
+  <si>
+    <t>package.json#scripts.server</t>
+  </si>
+  <si>
+    <t>hexo server</t>
+  </si>
+  <si>
+    <t>npm script: sync-themes</t>
+  </si>
+  <si>
+    <t>package.json#scripts.sync-themes</t>
+  </si>
+  <si>
+    <t>node tools/sync-themes.mjs</t>
+  </si>
+  <si>
+    <t>npm script: postinstall</t>
+  </si>
+  <si>
+    <t>package.json#scripts.postinstall</t>
+  </si>
+  <si>
+    <t>npm run sync-themes</t>
+  </si>
+  <si>
+    <t>npm script: doc:requirements</t>
+  </si>
+  <si>
+    <t>package.json#scripts.doc:requirements</t>
+  </si>
+  <si>
+    <t>node tools/write-requirements-xlsx.mjs</t>
+  </si>
+  <si>
+    <t>规范项</t>
+  </si>
+  <si>
+    <t>规则</t>
+  </si>
+  <si>
+    <t>示例</t>
+  </si>
+  <si>
+    <t>检查方式</t>
+  </si>
+  <si>
+    <t>Front-matter 必填</t>
+  </si>
+  <si>
+    <t>title/date/updated/tags/categories/keywords/description/cover/permalink</t>
+  </si>
+  <si>
+    <t>title: ...\ndate: 2026-02-09 02:51:48\ncover: /2026/02/09/.../cover.jpg\npermalink: /2026/02/09/.../</t>
+  </si>
+  <si>
+    <t>手动检查 + 本地 build</t>
+  </si>
+  <si>
+    <t>cover 建议用绝对路径，避免首页 404</t>
+  </si>
+  <si>
+    <t>标题层级</t>
+  </si>
+  <si>
+    <t>全文仅一个 H1（#）；二级 ##；三级 ###；禁止跳级</t>
+  </si>
+  <si>
+    <t># 标题\n## 小节\n### 子小节</t>
+  </si>
+  <si>
+    <t>手动检查</t>
+  </si>
+  <si>
+    <t>避免 TOC 锚点混乱</t>
+  </si>
+  <si>
+    <t>摘要截断</t>
+  </si>
+  <si>
+    <t>必须加入 &lt;!-- more --&gt;，首页摘要控制在 200 字以内</t>
+  </si>
+  <si>
+    <t>开头两段介绍\n\n&lt;!-- more --&gt;\n\n正文...</t>
+  </si>
+  <si>
+    <t>本地首页预览</t>
+  </si>
+  <si>
+    <t>图片（文章资源）</t>
+  </si>
+  <si>
+    <t>post_asset_folder=true 时，优先用 {% asset_img xxx.png "说明" %}</t>
+  </si>
+  <si>
+    <t>{% asset_img gameplay-1.png "战斗界面截图" class="full-width" %}</t>
+  </si>
+  <si>
+    <t>hexo generate 后检查 public 是否有对应图片</t>
+  </si>
+  <si>
+    <t>宽度 &gt; 800px 建议加 full-width</t>
+  </si>
+  <si>
+    <t>代码块</t>
+  </si>
+  <si>
+    <t>所有代码块标注语言（```cpp / ```python / ```js）</t>
+  </si>
+  <si>
+    <t>```js\nconsole.log('hi')\n```</t>
+  </si>
+  <si>
+    <t>本地文章页预览</t>
+  </si>
+  <si>
+    <t>保证高亮稳定</t>
+  </si>
+  <si>
+    <t>参考资料</t>
+  </si>
+  <si>
+    <t>文末统一用有序列表，格式 [title](url)，上线前确认可访问</t>
+  </si>
+  <si>
+    <t>1. [GitHub 仓库](https://github.com/...)</t>
+  </si>
+  <si>
+    <t>手动打开链接</t>
+  </si>
+  <si>
+    <t>扩展目标</t>
+  </si>
+  <si>
+    <t>修改点（文件/目录）</t>
+  </si>
+  <si>
+    <t>最小步骤</t>
+  </si>
+  <si>
+    <t>验证方式</t>
+  </si>
+  <si>
+    <t>风险/回滚</t>
+  </si>
+  <si>
+    <t>新增独立页面（如 /projects）</t>
+  </si>
+  <si>
+    <t>source/projects/index.md + _config.butterfly.yml#menu</t>
+  </si>
+  <si>
+    <t>npx hexo new page "projects" → 写内容 → menu 增加入口</t>
+  </si>
+  <si>
+    <t>npm run server 访问 /projects/</t>
+  </si>
+  <si>
+    <t>导航路径拼写错误；回滚删除目录与 menu 项</t>
+  </si>
+  <si>
+    <t>新增全站 CSS</t>
+  </si>
+  <si>
+    <t>source/css/*.css + _config.butterfly.yml#inject.head</t>
+  </si>
+  <si>
+    <t>新增 CSS 文件 → inject.head 引入</t>
+  </si>
+  <si>
+    <t>本地预览确认生效</t>
+  </si>
+  <si>
+    <t>覆盖主题样式导致布局异常；回滚移除注入</t>
+  </si>
+  <si>
+    <t>新增全站 JS（PJAX 兼容）</t>
+  </si>
+  <si>
+    <t>source/js/*.js + _config.butterfly.yml#inject.bottom</t>
+  </si>
+  <si>
+    <t>新增 JS 文件 → inject.bottom 引入 → 监听 pjax:complete 重新绑定</t>
+  </si>
+  <si>
+    <t>切换页面后功能仍正常</t>
+  </si>
+  <si>
+    <t>重复绑定事件/内存泄露；回滚移除注入</t>
+  </si>
+  <si>
+    <t>新增 Hexo 插件（如 sitemap）</t>
+  </si>
+  <si>
+    <t>package.json + _config.yml</t>
+  </si>
+  <si>
+    <t>npm i 插件 → 配置 → npm run build</t>
+  </si>
+  <si>
+    <t>public/ 生成对应文件；Actions 通过</t>
+  </si>
+  <si>
+    <t>Actions 构建失败；回滚依赖与配置</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>触发条件</t>
+  </si>
+  <si>
+    <t>产物</t>
+  </si>
+  <si>
+    <t>故障现象</t>
+  </si>
+  <si>
+    <t>处理办法</t>
+  </si>
+  <si>
+    <t>发布到线上（路线 B）</t>
+  </si>
+  <si>
+    <t>git commit + git push origin main</t>
+  </si>
+  <si>
+    <t>push main</t>
+  </si>
+  <si>
+    <t>Pages 未更新/站点 404</t>
+  </si>
+  <si>
+    <t>Settings→Pages Source 选 GitHub Actions；查看 Actions 日志</t>
+  </si>
+  <si>
+    <t>仅验证构建（PR）</t>
+  </si>
+  <si>
+    <t>提交 PR</t>
+  </si>
+  <si>
+    <t>pull_request</t>
+  </si>
+  <si>
+    <t>Actions 构建日志</t>
+  </si>
+  <si>
+    <t>构建失败</t>
+  </si>
+  <si>
+    <t>按日志定位依赖/配置/资源路径问题；本地先 npm run build 复现</t>
+  </si>
+  <si>
+    <t>首页封面显示 404</t>
+  </si>
+  <si>
+    <t>检查文章 front-matter cover 字段</t>
+  </si>
+  <si>
+    <t>首页卡片加载封面</t>
+  </si>
+  <si>
+    <t>封面图片请求</t>
+  </si>
+  <si>
+    <t>封面显示 404 图</t>
+  </si>
+  <si>
+    <t>cover 用站点绝对路径（以 / 开头）；重新 build</t>
+  </si>
+  <si>
     <t>npm install; npm run server</t>
-  </si>
-  <si>
-    <t>http://localhost:4000/</t>
-  </si>
-  <si>
-    <t>写完文章 push main 触发 Actions 自动发布</t>
-  </si>
-  <si>
-    <t>自动发布</t>
-  </si>
-  <si>
-    <t>GitHub Actions 构建并发布到 GitHub Pages</t>
-  </si>
-  <si>
-    <t>.github/workflows/pages.yml</t>
-  </si>
-  <si>
-    <t>线上站点</t>
-  </si>
-  <si>
-    <t>push main 自动发布；PR 仅构建验证</t>
-  </si>
-  <si>
-    <t>路径</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>归类</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>示例/关键点</t>
-  </si>
-  <si>
-    <t>是否发布(Y/N)</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>/source/_posts/</t>
-  </si>
-  <si>
-    <t>dir</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>文章 Markdown（可按年份分目录）</t>
-  </si>
-  <si>
-    <t>source/_posts/2026/2026-02-09-lei-xing-cun-zhe-you-xi.md</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>post_asset_folder=true 时，文章资源目录与 md 同级</t>
-  </si>
-  <si>
-    <t>/source/img/</t>
-  </si>
-  <si>
-    <t>全站静态图片（非文章私有资源）</t>
-  </si>
-  <si>
-    <t>首页 banner、头像、通用配图</t>
-  </si>
-  <si>
-    <t>适合被多篇文章复用的资源</t>
-  </si>
-  <si>
-    <t>/source/css/custom.css</t>
-  </si>
-  <si>
-    <t>file</t>
-  </si>
-  <si>
-    <t>自定义样式（字体/动态背景/深色模式等）</t>
-  </si>
-  <si>
-    <t>通过主题 inject 引入</t>
-  </si>
-  <si>
-    <t>路径为 /css/custom.css</t>
-  </si>
-  <si>
-    <t>/source/js/cloud-bg.js</t>
-  </si>
-  <si>
-    <t>动态背景脚本（页面类型识别 + PJAX 兼容）</t>
-  </si>
-  <si>
-    <t>路径为 /js/cloud-bg.js</t>
-  </si>
-  <si>
-    <t>/_config.yml</t>
-  </si>
-  <si>
-    <t>配置</t>
-  </si>
-  <si>
-    <t>Hexo 主配置</t>
-  </si>
-  <si>
-    <t>url=https://yurisachan16-creator.github.io; permalink=:year/:month/:day/:title/</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>改动会影响全站生成与路径</t>
-  </si>
-  <si>
-    <t>/_config.butterfly.yml</t>
-  </si>
-  <si>
-    <t>Butterfly 主题配置</t>
-  </si>
-  <si>
-    <t>menu、cover、inject、自定义资源</t>
-  </si>
-  <si>
-    <t>控制首页封面、导航菜单、注入资源等</t>
-  </si>
-  <si>
-    <t>/.github/workflows/pages.yml</t>
-  </si>
-  <si>
-    <t>自动化</t>
-  </si>
-  <si>
-    <t>Pages 构建与发布工作流</t>
-  </si>
-  <si>
-    <t>npm ci → npm run build → upload public</t>
-  </si>
-  <si>
-    <t>仓库 Settings → Pages 需要选择 GitHub Actions</t>
-  </si>
-  <si>
-    <t>/tools/</t>
-  </si>
-  <si>
-    <t>工具</t>
-  </si>
-  <si>
-    <t>本地脚本（不会发布到站点）</t>
-  </si>
-  <si>
-    <t>图片处理脚本、主题同步脚本等</t>
-  </si>
-  <si>
-    <t>不要把工具脚本放到 source/ 里</t>
-  </si>
-  <si>
-    <t>/doc/需求.xlsx</t>
-  </si>
-  <si>
-    <t>文档</t>
-  </si>
-  <si>
-    <t>结构/规范/扩展记录表</t>
-  </si>
-  <si>
-    <t>本脚本自动写入更新</t>
-  </si>
-  <si>
-    <t>本次生成时间：2026-02-14 00:04:05</t>
-  </si>
-  <si>
-    <t>/_config.butterfly.yml#menu</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>导航菜单项</t>
-  </si>
-  <si>
-    <t>首页: / || fas fa-home</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>归档: /archives/ || fas fa-archive</t>
-  </si>
-  <si>
-    <t>标签: /tags/ || fas fa-tags</t>
-  </si>
-  <si>
-    <t>分类: /categories/ || fas fa-folder-open</t>
-  </si>
-  <si>
-    <t>关于: /about/ || fas fa-heart</t>
-  </si>
-  <si>
-    <t>接口类型</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>入口（命令/文件#键）</t>
-  </si>
-  <si>
-    <t>输入</t>
-  </si>
-  <si>
-    <t>输出/影响</t>
-  </si>
-  <si>
-    <t>常见问题/排查</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>本地预览</t>
-  </si>
-  <si>
-    <t>npm run server</t>
-  </si>
-  <si>
-    <t>source/ + 配置</t>
-  </si>
-  <si>
-    <t>端口被占用/依赖未装/主题未同步</t>
-  </si>
-  <si>
-    <t>生成静态站点</t>
-  </si>
-  <si>
-    <t>npm run build</t>
-  </si>
-  <si>
-    <t>封面/图片路径写成相对路径导致首页 404</t>
-  </si>
-  <si>
-    <t>清理缓存</t>
-  </si>
-  <si>
-    <t>npm run clean</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>清理 db.json 与 public 等缓存</t>
-  </si>
-  <si>
-    <t>生成异常时优先 clean 后再 build</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>Actions 构建与发布</t>
-  </si>
-  <si>
-    <t>.github/workflows/pages.yml (push main)</t>
-  </si>
-  <si>
-    <t>main 分支源码</t>
-  </si>
-  <si>
-    <t>GitHub Pages</t>
-  </si>
-  <si>
-    <t>Settings→Pages 未设为 GitHub Actions/依赖安装失败/生成失败</t>
-  </si>
-  <si>
-    <t>永久链接规则</t>
-  </si>
-  <si>
-    <t>_config.yml#permalink</t>
-  </si>
-  <si>
-    <t>文章 date/title</t>
-  </si>
-  <si>
-    <t>文章 URL 结构</t>
-  </si>
-  <si>
-    <t>改规则会影响历史链接；可用 front-matter permalink 固定单篇路径</t>
-  </si>
-  <si>
-    <t>文章资源文件夹</t>
-  </si>
-  <si>
-    <t>_config.yml#post_asset_folder</t>
-  </si>
-  <si>
-    <t>文章同名目录资源</t>
-  </si>
-  <si>
-    <t>生成到 public 的文章资源</t>
-  </si>
-  <si>
-    <t>资源目录需与文章 md 同级；封面建议用以 / 开头的绝对路径</t>
-  </si>
-  <si>
-    <t>Front-matter</t>
-  </si>
-  <si>
-    <t>封面 cover</t>
-  </si>
-  <si>
-    <t>post.md front-matter#cover</t>
-  </si>
-  <si>
-    <t>图片路径</t>
-  </si>
-  <si>
-    <t>首页卡片封面/文章页封面</t>
-  </si>
-  <si>
-    <t>推荐使用站点绝对路径，如 /2026/02/09/.../cover.jpg</t>
-  </si>
-  <si>
-    <t>npm script: build</t>
-  </si>
-  <si>
-    <t>package.json#scripts.build</t>
-  </si>
-  <si>
-    <t>hexo generate</t>
-  </si>
-  <si>
-    <t>npm script: clean</t>
-  </si>
-  <si>
-    <t>package.json#scripts.clean</t>
-  </si>
-  <si>
-    <t>hexo clean</t>
-  </si>
-  <si>
-    <t>npm script: deploy</t>
-  </si>
-  <si>
-    <t>package.json#scripts.deploy</t>
-  </si>
-  <si>
-    <t>hexo deploy</t>
-  </si>
-  <si>
-    <t>npm script: server</t>
-  </si>
-  <si>
-    <t>package.json#scripts.server</t>
-  </si>
-  <si>
-    <t>hexo server</t>
-  </si>
-  <si>
-    <t>npm script: sync-themes</t>
-  </si>
-  <si>
-    <t>package.json#scripts.sync-themes</t>
-  </si>
-  <si>
-    <t>node tools/sync-themes.mjs</t>
-  </si>
-  <si>
-    <t>npm script: postinstall</t>
-  </si>
-  <si>
-    <t>package.json#scripts.postinstall</t>
-  </si>
-  <si>
-    <t>npm run sync-themes</t>
-  </si>
-  <si>
-    <t>npm script: doc:requirements</t>
-  </si>
-  <si>
-    <t>package.json#scripts.doc:requirements</t>
-  </si>
-  <si>
-    <t>node tools/write-requirements-xlsx.mjs</t>
-  </si>
-  <si>
-    <t>规范项</t>
-  </si>
-  <si>
-    <t>规则</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>检查方式</t>
-  </si>
-  <si>
-    <t>Front-matter 必填</t>
-  </si>
-  <si>
-    <t>title/date/updated/tags/categories/keywords/description/cover/permalink</t>
-  </si>
-  <si>
-    <t>title: ...\ndate: 2026-02-09 02:51:48\ncover: /2026/02/09/.../cover.jpg\npermalink: /2026/02/09/.../</t>
-  </si>
-  <si>
-    <t>手动检查 + 本地 build</t>
-  </si>
-  <si>
-    <t>cover 建议用绝对路径，避免首页 404</t>
-  </si>
-  <si>
-    <t>标题层级</t>
-  </si>
-  <si>
-    <t>全文仅一个 H1（#）；二级 ##；三级 ###；禁止跳级</t>
-  </si>
-  <si>
-    <t># 标题\n## 小节\n### 子小节</t>
-  </si>
-  <si>
-    <t>手动检查</t>
-  </si>
-  <si>
-    <t>避免 TOC 锚点混乱</t>
-  </si>
-  <si>
-    <t>摘要截断</t>
-  </si>
-  <si>
-    <t>必须加入 &lt;!-- more --&gt;，首页摘要控制在 200 字以内</t>
-  </si>
-  <si>
-    <t>开头两段介绍\n\n&lt;!-- more --&gt;\n\n正文...</t>
-  </si>
-  <si>
-    <t>本地首页预览</t>
-  </si>
-  <si>
-    <t>图片（文章资源）</t>
-  </si>
-  <si>
-    <t>post_asset_folder=true 时，优先用 {% asset_img xxx.png "说明" %}</t>
-  </si>
-  <si>
-    <t>{% asset_img gameplay-1.png "战斗界面截图" class="full-width" %}</t>
-  </si>
-  <si>
-    <t>hexo generate 后检查 public 是否有对应图片</t>
-  </si>
-  <si>
-    <t>宽度 &gt; 800px 建议加 full-width</t>
-  </si>
-  <si>
-    <t>代码块</t>
-  </si>
-  <si>
-    <t>所有代码块标注语言（```cpp / ```python / ```js）</t>
-  </si>
-  <si>
-    <t>```js\nconsole.log('hi')\n```</t>
-  </si>
-  <si>
-    <t>本地文章页预览</t>
-  </si>
-  <si>
-    <t>保证高亮稳定</t>
-  </si>
-  <si>
-    <t>参考资料</t>
-  </si>
-  <si>
-    <t>文末统一用有序列表，格式 [title](url)，上线前确认可访问</t>
-  </si>
-  <si>
-    <t>1. [GitHub 仓库](https://github.com/...)</t>
-  </si>
-  <si>
-    <t>手动打开链接</t>
-  </si>
-  <si>
-    <t>扩展目标</t>
-  </si>
-  <si>
-    <t>修改点（文件/目录）</t>
-  </si>
-  <si>
-    <t>最小步骤</t>
-  </si>
-  <si>
-    <t>验证方式</t>
-  </si>
-  <si>
-    <t>风险/回滚</t>
-  </si>
-  <si>
-    <t>新增独立页面（如 /projects）</t>
-  </si>
-  <si>
-    <t>source/projects/index.md + _config.butterfly.yml#menu</t>
-  </si>
-  <si>
-    <t>npx hexo new page "projects" → 写内容 → menu 增加入口</t>
-  </si>
-  <si>
-    <t>npm run server 访问 /projects/</t>
-  </si>
-  <si>
-    <t>导航路径拼写错误；回滚删除目录与 menu 项</t>
-  </si>
-  <si>
-    <t>新增全站 CSS</t>
-  </si>
-  <si>
-    <t>source/css/*.css + _config.butterfly.yml#inject.head</t>
-  </si>
-  <si>
-    <t>新增 CSS 文件 → inject.head 引入</t>
-  </si>
-  <si>
-    <t>本地预览确认生效</t>
-  </si>
-  <si>
-    <t>覆盖主题样式导致布局异常；回滚移除注入</t>
-  </si>
-  <si>
-    <t>新增全站 JS（PJAX 兼容）</t>
-  </si>
-  <si>
-    <t>source/js/*.js + _config.butterfly.yml#inject.bottom</t>
-  </si>
-  <si>
-    <t>新增 JS 文件 → inject.bottom 引入 → 监听 pjax:complete 重新绑定</t>
-  </si>
-  <si>
-    <t>切换页面后功能仍正常</t>
-  </si>
-  <si>
-    <t>重复绑定事件/内存泄露；回滚移除注入</t>
-  </si>
-  <si>
-    <t>新增 Hexo 插件（如 sitemap）</t>
-  </si>
-  <si>
-    <t>package.json + _config.yml</t>
-  </si>
-  <si>
-    <t>npm i 插件 → 配置 → npm run build</t>
-  </si>
-  <si>
-    <t>public/ 生成对应文件；Actions 通过</t>
-  </si>
-  <si>
-    <t>Actions 构建失败；回滚依赖与配置</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>操作</t>
-  </si>
-  <si>
-    <t>触发条件</t>
-  </si>
-  <si>
-    <t>产物</t>
-  </si>
-  <si>
-    <t>故障现象</t>
-  </si>
-  <si>
-    <t>处理办法</t>
-  </si>
-  <si>
-    <t>发布到线上（路线 B）</t>
-  </si>
-  <si>
-    <t>git commit + git push origin main</t>
-  </si>
-  <si>
-    <t>push main</t>
-  </si>
-  <si>
-    <t>Pages 未更新/站点 404</t>
-  </si>
-  <si>
-    <t>Settings→Pages Source 选 GitHub Actions；查看 Actions 日志</t>
-  </si>
-  <si>
-    <t>仅验证构建（PR）</t>
-  </si>
-  <si>
-    <t>提交 PR</t>
-  </si>
-  <si>
-    <t>pull_request</t>
-  </si>
-  <si>
-    <t>Actions 构建日志</t>
-  </si>
-  <si>
-    <t>构建失败</t>
-  </si>
-  <si>
-    <t>按日志定位依赖/配置/资源路径问题；本地先 npm run build 复现</t>
-  </si>
-  <si>
-    <t>首页封面显示 404</t>
-  </si>
-  <si>
-    <t>检查文章 front-matter cover 字段</t>
-  </si>
-  <si>
-    <t>首页卡片加载封面</t>
-  </si>
-  <si>
-    <t>封面图片请求</t>
-  </si>
-  <si>
-    <t>封面显示 404 图</t>
-  </si>
-  <si>
-    <t>cover 用站点绝对路径（以 / 开头）；重新 build</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1068,87 +1069,87 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1173,82 +1174,82 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -1370,30 +1371,30 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1420,347 +1421,347 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1786,302 +1787,302 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2106,121 +2107,121 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
